--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_463_Malaysia_Sarawak.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_463_Malaysia_Sarawak.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rba9ed7c4749149a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rc205e12bf03b4286"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R706d16765484401b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rd7f6322bad8d4a67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R214c8c3d05384873"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R6fbc1c35cd454fa0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R07a2352872f648be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R2b0e8be09e16470d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rc0349089bf99413f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R42c9defa3e40412a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Ra143b402c5dc4787"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R4867205d11ff4b5a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ463CommercialTable" displayName="EEZ463CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ463CommercialTable" displayName="EEZ463CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ463FunctionalTable" displayName="EEZ463FunctionalTable" ref="A1:O21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O21"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ463FunctionalTable" displayName="EEZ463FunctionalTable" ref="A1:E21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E21"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ463ValidationTable" displayName="EEZ463ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ463ValidationTable" displayName="EEZ463ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -10208,7 +10162,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc97e69af43d64620"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R523775be4d73455f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10218,20 +10172,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -10239,606 +10183,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>8579.877043266</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.3294539657110174</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>213.52757393764534</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>8579.877043266</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>220.6827399831043</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$143,A2,'Species'!$U$2:$U$143))</x:f>
-        <x:v>1893430.7746260767</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.3294539657110174</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>213.52757393764534</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>1832040.3297318867</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>61390.444894189946</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0335093304977485</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.033509330497748506</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>11646.5252390744</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.997594521208414</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>99.44764913730054</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>11646.5252390744</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>183.76038463943283</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$143,A3,'Species'!$U$2:$U$143))</x:f>
-        <x:v>2140169.957645174</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.997594521208414</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>99.44764913730054</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1158219.5556441864</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>981950.4020009877</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.8478102422082139</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.847810242208214</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>1600.043468806</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.67441899313746</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>472.5186920372207</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>1600.043468806</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>595.6684060440185</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$143,A4,'Species'!$U$2:$U$143))</x:f>
-        <x:v>953095.3426648123</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.67441899313746</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>472.5186920372207</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>756050.4470829087</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>197044.89558190363</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.2606240051072883</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.26062400510728834</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>8060.7586780151005</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.5811819998555148</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>381.22555017318194</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>8060.7586780151005</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>654.4427576431997</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$143,A5,'Species'!$U$2:$U$143))</x:f>
-        <x:v>5275305.137936555</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.5811819998555148</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>381.22555017318194</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>3072967.1618395573</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>2202337.9760969975</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.7166812595480587</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.7166812595480588</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>136.4364414017</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.0590895562309757</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>11.457491829911516</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>136.4364414017</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>11.529978767984005</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$143,A6,'Species'!$U$2:$U$143))</x:f>
-        <x:v>1573.1092725408948</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.0590895562309757</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>11.457491829911516</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>1563.2194126621791</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>9.889859878715697</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.006326597404438</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.006326597404438038</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>43867.52696715051</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.6324994575701255</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>429.04165336941156</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>43867.52696715051</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>758.9297820651299</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$143,A7,'Species'!$U$2:$U$143))</x:f>
-        <x:v>33292372.680915743</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.6324994575701255</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>429.04165336941156</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>18820996.299213503</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>14471376.38170224</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.7688953417575972</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.7688953417575973</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>85665.48761580548</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.7434087548705937</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>553.8711635619485</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>85665.48761580548</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>861.9645486040652</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$143,A8,'Species'!$U$2:$U$143))</x:f>
-        <x:v>73840613.3637049</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.7434087548705937</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>553.8711635619485</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>47447643.302867875</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>26392970.06083703</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.5562546045198784</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.5562546045198785</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>632.238736931</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.9061266530546526</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>805.6133475104708</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>632.238736931</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>805.7959618895422</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$143,A9,'Species'!$U$2:$U$143))</x:f>
-        <x:v>509455.42116914433</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.9061266530546526</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>805.6133475104708</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>509339.9652847748</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>115.45588436955586</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0002266774497168</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.0002266774497167208</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>6148.655089743501</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.9959495693314966</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>990.7168952700653</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>6148.655089743501</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1103.7763680431474</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$143,A10,'Species'!$U$2:$U$143))</x:f>
-        <x:v>6786740.1833070945</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.9959495693314966</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>990.7168952700653</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>6091576.480597165</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>695163.7027099291</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.114118850009379</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.11411885000937906</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>6080.4538436333005</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.474241921625594</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>2980.1760596987133</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>6080.4538436333005</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2989.6765324272615</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$143,A11,'Species'!$U$2:$U$143))</x:f>
-        <x:v>18178590.16281762</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.474241921625594</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>2980.1760596987133</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>18120822.976898987</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>57767.185918632895</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0031878897549122</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.003187889754912146</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6084bbb4c36843ad"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R214ccce79d4644c9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10848,20 +10398,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -10869,1146 +10409,402 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>1133.3681740447996</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.7160647404672336</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>520.0735183407568</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>1133.3681740447996</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>529.9640055884482</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$143,A2,'Species'!$U$2:$U$143))</x:f>
-        <x:v>600644.3373232476</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.7160647404672336</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>520.0735183407568</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>589434.7738509182</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>11209.563472329406</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0190174790657407</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.019017479065740642</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>6444.3243541336005</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.46</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>288.40315031266056</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>6444.3243541336005</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>288.40315031266056</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$143,A3,'Species'!$U$2:$U$143))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1858563.4453687319</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.46</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>288.40315031266056</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>1858563.4453687319</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>4891.7428427829</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.4085844530530105</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2562.031429154864</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>4891.7428427829</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2583.5376839864853</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$143,A4,'Species'!$U$2:$U$143))</x:f>
-        <x:v>12638001.9747008</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.4085844530530105</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2562.031429154864</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>12532798.90655315</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>105203.06814764999</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0083942197534697</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.008394219753469547</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>1513.0768696227</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.014667356106169</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1034.349612549917</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>1513.0768696227</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1065.3710124037548</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$143,A5,'Species'!$U$2:$U$143))</x:f>
-        <x:v>1611988.23643464</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.014667356106169</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1034.349612549917</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>1565050.4738524812</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>46937.76258215867</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0299912132971776</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.02999121329717762</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>16209.9366729208</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.394144376593754</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2478.2457872297264</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>16209.9366729208</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2514.756763336087</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$143,A6,'Species'!$U$2:$U$143))</x:f>
-        <x:v>40764047.881477244</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.394144376593754</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2478.2457872297264</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>40172207.27092662</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>591840.6105506271</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.014732588791031</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.01473258879103099</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>3958.2290307363</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.84988496044795</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>707.7582826226167</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>3958.2290307363</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>707.783721685895</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$143,A7,'Species'!$U$2:$U$143))</x:f>
-        <x:v>2801570.074659691</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.84988496044795</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>707.7582826226167</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>2801469.3810209082</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>100.69363878294826</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0000359431516421</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.00003594315164217629</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>1042.6896163744998</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.595463203574985</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>393.97004637001</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>1042.6896163744998</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>464.03434899072016</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$143,A8,'Species'!$U$2:$U$143))</x:f>
-        <x:v>483843.79733372474</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.595463203574985</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>393.97004637001</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>410788.4765125896</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>73055.32082113513</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.1778416995562828</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.17784169955628287</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>2190.4260590072</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.259896929192641</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1819.2690415141788</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>2190.4260590072</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1819.3584267590677</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$143,A9,'Species'!$U$2:$U$143))</x:f>
-        <x:v>3985170.108647404</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.259896929192641</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1819.2690415141788</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>3984974.3168777083</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>195.79176969546825</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0000491325047858</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.000049132504785846216</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>1427.8170825619</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>2.805346547258482</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>63.877299469962814</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>1427.8170825619</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>85.1883153907353</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$143,A10,'Species'!$U$2:$U$143))</x:f>
-        <x:v>121633.33194956266</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>2.805346547258482</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>63.877299469962814</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>91205.0993711351</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>30428.23257842756</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.333624246760676</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.3336242467606761</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>9763.932997004102</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.569214769703211</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>370.86407819164725</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>9763.932997004102</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>442.189332360314</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$143,A11,'Species'!$U$2:$U$143))</x:f>
-        <x:v>4317507.013156083</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.569214769703211</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>370.86407819164725</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>3621092.0104589337</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>696415.0026971498</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.192321819132369</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.19232181913236907</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>36991.9560258757</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.6669254588506</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>464.4355538985627</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>36991.9560258757</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>837.7983532152097</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$143,A12,'Species'!$U$2:$U$143))</x:f>
-        <x:v>30991799.84068811</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.6669254588506</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>464.4355538985627</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>17180379.586668853</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>13811420.254019257</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.8039065833409322</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.8039065833409323</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>23704.942009689395</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.6493018420746273</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>445.96609475547257</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>23704.942009689395</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>732.6010965386312</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$143,A13,'Species'!$U$2:$U$143))</x:f>
-        <x:v>17366266.509683114</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.6493018420746273</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>445.96609475547257</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>10571600.414466124</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>6794666.0952169895</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.6427282368636638</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.6427282368636638</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>15495.275411976101</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.76087577386457</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>576.6015079866373</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>15495.275411976101</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>732.207729462516</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$143,A14,'Species'!$U$2:$U$143))</x:f>
-        <x:v>11345760.426799374</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.76087577386457</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>576.6015079866373</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>8934599.169213682</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>2411161.2575856913</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.2698678711736648</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.2698678711736649</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>143.6183736701</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.077637696115294</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>11.957425841623037</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>143.6183736701</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>12.299355813601512</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$143,A15,'Species'!$U$2:$U$143))</x:f>
-        <x:v>1766.4134791393387</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.077637696115294</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>11.957425841623037</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>1717.3060526547272</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>49.10742648461155</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0285956171928108</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.028595617192810792</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>10218.7081565125</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.0244565214817745</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>105.79289982614135</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>10218.7081565125</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>197.533445008817</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$143,A16,'Species'!$U$2:$U$143))</x:f>
-        <x:v>2018536.625695612</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.0244565214817745</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>105.79289982614135</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>1081066.7683545006</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>937469.8573411114</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.8671710987546504</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.8671710987546504</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>3288.7497374742</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.2310489931115924</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>170.2350541103807</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>3288.7497374742</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>171.02420888429225</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$143,A17,'Species'!$U$2:$U$143))</x:f>
-        <x:v>562455.8220699489</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.2310489931115924</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>170.2350541103807</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>559860.4895144207</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>2595.332555528148</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0046356772877099</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.004635677287709902</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>7869.9213549731985</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.7157227330174605</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>519.6641210137022</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>7869.9213549731985</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>525.3077495944879</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$143,A18,'Species'!$U$2:$U$143))</x:f>
-        <x:v>4134130.6764665735</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.7157227330174605</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>519.6641210137022</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>4089715.763379112</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>44414.91308746161</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0108601466843172</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.01086014668431724</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>14464.680882775001</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.292934506756581</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>196.3064217036335</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>14464.680882775001</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>206.7244755456445</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$143,A19,'Species'!$U$2:$U$143))</x:f>
-        <x:v>2990203.569426772</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.292934506756581</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>196.3064217036335</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>2839509.745182515</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>150693.82424425706</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.0530703669884995</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.0530703669884996</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>10064.564002886</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.498935703734871</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>315.4537567018078</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>10064.564002886</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>330.3034989972608</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$143,A20,'Species'!$U$2:$U$143))</x:f>
-        <x:v>3324360.706035123</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.498935703734871</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>315.4537567018078</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>3174904.5242761727</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>149456.18175895046</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.047074228725988</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.04707422872598793</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>1600.043468806</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.67441899313746</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>472.5186920372207</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>1600.043468806</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>595.6684060440185</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$143,A21,'Species'!$U$2:$U$143))</x:f>
-        <x:v>953095.3426648123</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.67441899313746</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>472.5186920372207</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>756050.4470829087</x:v>
       </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>197044.89558190363</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.2606240051072883</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.26062400510728834</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G21">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O21">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6920226b0ba34221"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbadef5e2f69a4152"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12183,7 +10979,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -12282,7 +11078,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>142871346.1340597</x:v>
+        <x:v>97811219.7385735</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -12296,7 +11092,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>142871346.13405973</x:v>
+        <x:v>116816988.36898412</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -12310,7 +11106,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-2.9802322387695312e-8</x:v>
+        <x:v>-45060126.39548622</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -12324,7 +11120,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-26054357.76507561</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -12335,9 +11131,9 @@
         <x:v>EEZ_463</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -12349,47 +11145,19 @@
         <x:v>EEZ_463</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_463</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_463</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f15aff52e764a28"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb4d24d3e75b4486"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12436,7 +11204,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
